--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="79">
   <si>
     <t>Dự án</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -255,9 +255,6 @@
   <si>
     <t xml:space="preserve">15h50
 24/02/2026</t>
-  </si>
-  <si>
-    <t>ẢNH BIÊN BẢN GỐC</t>
   </si>
   <si>
     <t>STT</t>
@@ -291,7 +288,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -350,12 +347,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -433,7 +424,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -488,21 +479,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF1A3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF1A3A6B"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF1A3A6B"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF1A3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -520,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -588,13 +564,10 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -612,50 +585,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="8096250" cy="10477500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -980,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2213,83 +2142,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -2298,11 +2152,9 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2321,31 +2173,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2494,31 +2346,31 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="25">
-        <v>30</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="A7" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="24">
+        <v>30</v>
+      </c>
+      <c r="E7" s="24">
         <v>-9.55</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <v>-63</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="24">
         <v>15</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <v>53.45</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="24">
         <v>3.56</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>D2000</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="80">
   <si>
     <t>Dự án</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>D2000</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -255,6 +255,9 @@
   <si>
     <t xml:space="preserve">15h50
 24/02/2026</t>
+  </si>
+  <si>
+    <t>⚠️ CẢNH BÁO: THIẾU HÌNH ẢNH BIÊN BẢN GỐC TRONG DỮ LIỆU</t>
   </si>
   <si>
     <t>STT</t>
@@ -288,7 +291,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -351,12 +354,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF991B1B"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF1E3A6E"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,11 +429,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -479,6 +493,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF991B1B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF991B1B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF991B1B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF991B1B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -496,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -565,9 +594,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -909,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2142,8 +2174,23 @@
         <v>30</v>
       </c>
     </row>
+    <row r="43" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -2152,6 +2199,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2173,31 +2221,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2346,31 +2394,31 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="24">
-        <v>30</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="A7" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="25">
+        <v>30</v>
+      </c>
+      <c r="E7" s="25">
         <v>-9.55</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>-63</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>15</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <v>53.45</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <v>3.56</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1500</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -257,7 +257,7 @@
 24/02/2026</t>
   </si>
   <si>
-    <t>⚠️ CẢNH BÁO: THIẾU HÌNH ẢNH BIÊN BẢN GỐC TRONG DỮ LIỆU</t>
+    <t>ẢNH BIÊN BẢN GỐC</t>
   </si>
   <si>
     <t>STT</t>
@@ -354,7 +354,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF991B1B"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -365,7 +365,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,11 +429,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
@@ -493,16 +488,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF991B1B"/>
+        <color rgb="FF1A3A6B"/>
       </left>
       <right style="thin">
-        <color rgb="FF991B1B"/>
+        <color rgb="FF1A3A6B"/>
       </right>
       <top style="thin">
-        <color rgb="FF991B1B"/>
+        <color rgb="FF1A3A6B"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF991B1B"/>
+        <color rgb="FF1A3A6B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -593,13 +588,13 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -617,6 +612,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="8096250" cy="10477500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2189,6 +2228,66 @@
       <c r="J43" s="23"/>
       <c r="K43" s="23"/>
     </row>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -2203,6 +2302,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1500</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>D1000</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
+++ b/SGC-CKN/Excel/fpqo8w_Cọc_khoan_nhồi_-_Trụ_HN478_C6_D2000_24-02-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="78">
   <si>
     <t>Dự án</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1000</t>
+    <t>D2000</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -162,9 +162,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám ghi, trạng thái dẻo cứng</t>
-  </si>
-  <si>
     <t xml:space="preserve">03h19
 24/02/2026</t>
   </si>
@@ -174,9 +171,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>Cát, sạn, sỏi nhỏ màu xám ghi, kết cấu chặt vừa</t>
   </si>
   <si>
     <t xml:space="preserve">03h58
@@ -291,7 +285,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -342,11 +336,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF4C1D95"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -365,7 +354,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,11 +404,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -579,22 +563,13 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1556,13 +1531,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" s="13">
         <v>-26.55</v>
@@ -1591,13 +1566,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="E23" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="F23" s="13">
         <v>-28.31</v>
@@ -1619,614 +1594,614 @@
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="16">
+      <c r="F24" s="13">
         <v>-29.34</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="13">
         <v>-31.17</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="13">
         <v>0.4</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="13">
         <v>1.83</v>
       </c>
       <c r="J24" s="8">
         <v>4.58</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="E25" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="16">
+      <c r="F25" s="13">
         <v>-31.17</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="13">
         <v>-33.2</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="13">
         <v>0.53</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="13">
         <v>2.03</v>
       </c>
       <c r="J25" s="8">
         <v>3.81</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="17" t="s">
+      <c r="A26" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="16">
+      <c r="E26" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="13">
         <v>-33.2</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="13">
         <v>-35.02</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="13">
         <v>0.53</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="13">
         <v>1.82</v>
       </c>
       <c r="J26" s="8">
         <v>3.41</v>
       </c>
-      <c r="K26" s="17" t="s">
+      <c r="K26" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="F27" s="16">
+        <v>-35.02</v>
+      </c>
+      <c r="G27" s="16">
+        <v>-36.98</v>
+      </c>
+      <c r="H27" s="16">
+        <v>1.97</v>
+      </c>
+      <c r="I27" s="16">
+        <v>1.96</v>
+      </c>
+      <c r="J27" s="19">
+        <v>1</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="19">
-        <v>-35.02</v>
-      </c>
-      <c r="G27" s="19">
+      <c r="F28" s="16">
         <v>-36.98</v>
       </c>
-      <c r="H27" s="19">
-        <v>1.97</v>
-      </c>
-      <c r="I27" s="19">
-        <v>1.96</v>
-      </c>
-      <c r="J27" s="22">
-        <v>1</v>
-      </c>
-      <c r="K27" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="19">
-        <v>-36.98</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="G28" s="16">
         <v>-39.01</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="16">
         <v>0.42</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="16">
         <v>2.03</v>
       </c>
       <c r="J28" s="8">
         <v>4.87</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="E29" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="16">
         <v>-39.01</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="16">
         <v>-41.03</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="16">
         <v>0.42</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="16">
         <v>2.02</v>
       </c>
       <c r="J29" s="8">
         <v>4.85</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="19">
+      <c r="A30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="16">
         <v>-41.03</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="16">
         <v>-43.02</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="16">
         <v>0.42</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="16">
         <v>1.99</v>
       </c>
       <c r="J30" s="8">
         <v>4.78</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="A31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="16">
         <v>-43.02</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="16">
         <v>-45.28</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="16">
         <v>0.42</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="16">
         <v>2.26</v>
       </c>
       <c r="J31" s="9">
         <v>5.42</v>
       </c>
-      <c r="K31" s="20" t="s">
+      <c r="K31" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F32" s="19">
+      <c r="A32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="16">
         <v>-45.28</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="16">
         <v>-47.12</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="16">
         <v>0.47</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="16">
         <v>1.84</v>
       </c>
       <c r="J32" s="8">
         <v>3.94</v>
       </c>
-      <c r="K32" s="20" t="s">
+      <c r="K32" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="19">
+      <c r="A33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="16">
         <v>-47.12</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="16">
         <v>-49.3</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="16">
         <v>0.4</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="16">
         <v>2.18</v>
       </c>
       <c r="J33" s="9">
         <v>5.45</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="19">
+      <c r="A34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="16">
         <v>-49.3</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="16">
         <v>-51.21</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="16">
         <v>0.63</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="16">
         <v>1.91</v>
       </c>
       <c r="J34" s="8">
         <v>3.02</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="K34" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="19">
+      <c r="A35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="16">
         <v>-51.21</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="16">
         <v>-53.32</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="16">
         <v>0.83</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="16">
         <v>2.11</v>
       </c>
       <c r="J35" s="8">
         <v>2.53</v>
       </c>
-      <c r="K35" s="20" t="s">
+      <c r="K35" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" s="19">
+      <c r="A36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="16">
         <v>-53.32</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="16">
         <v>-55.2</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="16">
         <v>0.67</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="16">
         <v>1.88</v>
       </c>
       <c r="J36" s="8">
         <v>2.82</v>
       </c>
-      <c r="K36" s="20" t="s">
+      <c r="K36" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" s="19">
+      <c r="A37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="16">
         <v>-55.2</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="16">
         <v>-57.2</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="16">
         <v>0.33</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="16">
         <v>2</v>
       </c>
       <c r="J37" s="9">
         <v>6</v>
       </c>
-      <c r="K37" s="20" t="s">
+      <c r="K37" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="19">
+      <c r="A38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="16">
         <v>-57.2</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="16">
         <v>-59.5</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="16">
         <v>0.67</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="16">
         <v>2.3</v>
       </c>
       <c r="J38" s="8">
         <v>3.45</v>
       </c>
-      <c r="K38" s="20" t="s">
+      <c r="K38" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="19">
+      <c r="A39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="16">
         <v>-59.5</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="16">
         <v>-61.5</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="16">
         <v>0.83</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="16">
         <v>2</v>
       </c>
       <c r="J39" s="8">
         <v>2.4</v>
       </c>
-      <c r="K39" s="20" t="s">
+      <c r="K39" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="19">
+      <c r="A40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="16">
         <v>-61.5</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="16">
         <v>-63</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="16">
         <v>0.83</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="16">
         <v>1.5</v>
       </c>
       <c r="J40" s="8">
         <v>1.8</v>
       </c>
-      <c r="K40" s="20" t="s">
+      <c r="K40" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
+      <c r="A43" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2308,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2321,31 +2296,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2414,25 +2389,25 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D4" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" s="13">
         <v>-26.55</v>
       </c>
       <c r="F4" s="13">
-        <v>-29.34</v>
+        <v>-35.02</v>
       </c>
       <c r="G4" s="13">
-        <v>0.7</v>
+        <v>2.17</v>
       </c>
       <c r="H4" s="13">
-        <v>2.79</v>
+        <v>8.47</v>
       </c>
       <c r="I4" s="8">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2443,82 +2418,53 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" s="16">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E5" s="16">
-        <v>-29.34</v>
+        <v>-35.02</v>
       </c>
       <c r="F5" s="16">
-        <v>-35.02</v>
+        <v>-63</v>
       </c>
       <c r="G5" s="16">
-        <v>1.47</v>
+        <v>9.3</v>
       </c>
       <c r="H5" s="16">
-        <v>5.68</v>
+        <v>27.98</v>
       </c>
       <c r="I5" s="8">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="19">
-        <v>14</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-35.02</v>
-      </c>
-      <c r="F6" s="19">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="22">
+        <v>30</v>
+      </c>
+      <c r="E6" s="22">
+        <v>-9.55</v>
+      </c>
+      <c r="F6" s="22">
         <v>-63</v>
       </c>
-      <c r="G6" s="19">
-        <v>9.3</v>
-      </c>
-      <c r="H6" s="19">
-        <v>27.98</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="25">
-        <v>30</v>
-      </c>
-      <c r="E7" s="25">
-        <v>-9.55</v>
-      </c>
-      <c r="F7" s="25">
-        <v>-63</v>
-      </c>
-      <c r="G7" s="25">
+      <c r="G6" s="22">
         <v>15</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H6" s="22">
         <v>53.45</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I6" s="22">
         <v>3.56</v>
       </c>
     </row>
